--- a/www/flightdata/xlsx/eoss-339.xlsx
+++ b/www/flightdata/xlsx/eoss-339.xlsx
@@ -3858,7 +3858,7 @@
         <v>29633.57</v>
       </c>
       <c r="I2">
-        <v>687</v>
+        <v>506</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
